--- a/franquias/pwr_reports/Keys Summary - Franquias (Stores)(2026-08-03 - 2026-08-06).xlsx
+++ b/franquias/pwr_reports/Keys Summary - Franquias (Stores)(2026-08-03 - 2026-08-06).xlsx
@@ -935,7 +935,7 @@
     <t>6.8</t>
   </si>
   <si>
-    <t>11.5</t>
+    <t>11.4</t>
   </si>
   <si>
     <t>18.0</t>
@@ -1765,7 +1765,7 @@
         <v>3.8163064864864866</v>
       </c>
       <c r="AC3" s="8">
-        <v>8.0038630000000008</v>
+        <v>7.9176010000000003</v>
       </c>
       <c r="AD3" s="8">
         <v>13.563628125000001</v>
@@ -1896,7 +1896,7 @@
         <v>5.7683732283464568</v>
       </c>
       <c r="AC4" s="8">
-        <v>8.6301869999999994</v>
+        <v>9.4371050000000007</v>
       </c>
       <c r="AD4" s="8">
         <v>16.3384125</v>
@@ -2027,7 +2027,7 @@
         <v>4.3989583333333337</v>
       </c>
       <c r="AC5" s="8">
-        <v>8.2049009999999996</v>
+        <v>8.1364579999999993</v>
       </c>
       <c r="AD5" s="8">
         <v>15.054860416666665</v>
@@ -2158,7 +2158,7 @@
         <v>3.5448444915254238</v>
       </c>
       <c r="AC6" s="8">
-        <v>6.9676689999999999</v>
+        <v>6.8726880000000001</v>
       </c>
       <c r="AD6" s="8">
         <v>14.3834</v>
@@ -2289,7 +2289,7 @@
         <v>4.965600581395349</v>
       </c>
       <c r="AC7" s="8">
-        <v>8.2690959999999993</v>
+        <v>8.4334030000000002</v>
       </c>
       <c r="AD7" s="8">
         <v>15.283716666666667</v>
@@ -2420,7 +2420,7 @@
         <v>10.173298979591836</v>
       </c>
       <c r="AC8" s="8">
-        <v>16.073222999999999</v>
+        <v>15.271235000000001</v>
       </c>
       <c r="AD8" s="8">
         <v>21.42548076923077</v>
@@ -2813,7 +2813,7 @@
         <v>5.5913276422764229</v>
       </c>
       <c r="AC11" s="8">
-        <v>10.679285999999999</v>
+        <v>11.938549</v>
       </c>
       <c r="AD11" s="8">
         <v>18.659230278884461</v>
@@ -3039,7 +3039,7 @@
         <v>6.4281312101910828</v>
       </c>
       <c r="AC13" s="8">
-        <v>14.030143000000001</v>
+        <v>14.116390000000001</v>
       </c>
       <c r="AD13" s="8">
         <v>20.905240251572327</v>
@@ -3301,7 +3301,7 @@
         <v>7.3254048543689319</v>
       </c>
       <c r="AC15" s="8">
-        <v>11.552476</v>
+        <v>11.448950999999999</v>
       </c>
       <c r="AD15" s="8">
         <v>18.976634579439253</v>
@@ -3563,7 +3563,7 @@
         <v>9.2935746987951813</v>
       </c>
       <c r="AC17" s="8">
-        <v>15.3597</v>
+        <v>15.565858</v>
       </c>
       <c r="AD17" s="8">
         <v>22.704680898876404</v>
@@ -3690,7 +3690,7 @@
         <v>1.8625</v>
       </c>
       <c r="AC18" s="8">
-        <v>3.980302</v>
+        <v>3.8250000000000002</v>
       </c>
       <c r="AD18" s="8">
         <v>10.794097916666667</v>
@@ -3954,7 +3954,7 @@
         <v>4.3810047794117644</v>
       </c>
       <c r="AC20" s="8">
-        <v>6.6148860000000003</v>
+        <v>6.4439190000000002</v>
       </c>
       <c r="AD20" s="8">
         <v>12.324756934306569</v>
@@ -4345,7 +4345,7 @@
         <v>3.3132352941176473</v>
       </c>
       <c r="AC23" s="8">
-        <v>6.2812799999999998</v>
+        <v>6.4719100000000003</v>
       </c>
       <c r="AD23" s="8">
         <v>14.044293150684933</v>
@@ -4476,7 +4476,7 @@
         <v>8.3509916666666673</v>
       </c>
       <c r="AC24" s="8">
-        <v>7.7376009999999997</v>
+        <v>10.774016</v>
       </c>
       <c r="AD24" s="8">
         <v>17.256666315789474</v>
@@ -4607,7 +4607,7 @@
         <v>8.5550857731958754</v>
       </c>
       <c r="AC25" s="8">
-        <v>12.660992999999999</v>
+        <v>11.484721</v>
       </c>
       <c r="AD25" s="8">
         <v>17.763457760314342</v>
@@ -5000,7 +5000,7 @@
         <v>9.2981317757009343</v>
       </c>
       <c r="AC28" s="8">
-        <v>18.951661999999999</v>
+        <v>17.148277</v>
       </c>
       <c r="AD28" s="8">
         <v>23.397049557522124</v>
@@ -5262,7 +5262,7 @@
         <v>3.2374454545454543</v>
       </c>
       <c r="AC30" s="8">
-        <v>9.6766819999999996</v>
+        <v>9.0497720000000008</v>
       </c>
       <c r="AD30" s="8">
         <v>16.679776219512195</v>
@@ -5522,7 +5522,7 @@
         <v>6.8060708609271519</v>
       </c>
       <c r="AC32" s="8">
-        <v>12.733924</v>
+        <v>12.292375</v>
       </c>
       <c r="AD32" s="8">
         <v>18.908494193548389</v>
@@ -5911,7 +5911,7 @@
         <v>6.0707360465116276</v>
       </c>
       <c r="AC35" s="8">
-        <v>8.1090820000000008</v>
+        <v>8.5530810000000006</v>
       </c>
       <c r="AD35" s="8">
         <v>16.071666666666665</v>
@@ -6397,7 +6397,7 @@
         <v>7.2602150537634413</v>
       </c>
       <c r="AC39" s="8">
-        <v>12.955774999999999</v>
+        <v>12.217484000000001</v>
       </c>
       <c r="AD39" s="8">
         <v>19.056028723404253</v>
@@ -6657,7 +6657,7 @@
         <v>3.4161320512820512</v>
       </c>
       <c r="AC41" s="8">
-        <v>7.6123409999999998</v>
+        <v>7.5989469999999999</v>
       </c>
       <c r="AD41" s="8">
         <v>15.829424074074074</v>
@@ -7145,7 +7145,7 @@
         <v>5.8260679487179488</v>
       </c>
       <c r="AC45" s="8">
-        <v>9.7367469999999994</v>
+        <v>9.7828579999999992</v>
       </c>
       <c r="AD45" s="8">
         <v>17.39362222222222</v>
@@ -7274,7 +7274,7 @@
         <v>6.1037037037037045</v>
       </c>
       <c r="AC46" s="8">
-        <v>6.8924219999999998</v>
+        <v>8.4623050000000006</v>
       </c>
       <c r="AD46" s="8">
         <v>14.104033870967742</v>
@@ -7663,7 +7663,7 @@
         <v>12.084415584415584</v>
       </c>
       <c r="AC49" s="8">
-        <v>17.876759</v>
+        <v>17.459026999999999</v>
       </c>
       <c r="AD49" s="8">
         <v>23.793332499999998</v>
@@ -8147,7 +8147,7 @@
         <v>6.5925082568807341</v>
       </c>
       <c r="AC53" s="8">
-        <v>9.5620969999999996</v>
+        <v>10.536446</v>
       </c>
       <c r="AD53" s="8">
         <v>18.507339449541284</v>
@@ -8536,7 +8536,7 @@
         <v>3.7048715384615387</v>
       </c>
       <c r="AC56" s="8">
-        <v>5.9757809999999996</v>
+        <v>5.8753190000000002</v>
       </c>
       <c r="AD56" s="8">
         <v>12.786538461538461</v>
@@ -8887,7 +8887,7 @@
         <v>4.7591207547169807</v>
       </c>
       <c r="AC59" s="8">
-        <v>10.887468</v>
+        <v>10.265139</v>
       </c>
       <c r="AD59" s="8">
         <v>16.981790740740742</v>
@@ -9016,7 +9016,7 @@
         <v>9.8153225806451605</v>
       </c>
       <c r="AC60" s="8">
-        <v>12.870585999999999</v>
+        <v>15.196787</v>
       </c>
       <c r="AD60" s="8">
         <v>22.561786428571427</v>
@@ -9276,7 +9276,7 @@
         <v>11.514542156862746</v>
       </c>
       <c r="AC62" s="8">
-        <v>16.136505</v>
+        <v>16.092907</v>
       </c>
       <c r="AD62" s="8">
         <v>22.716666346153847</v>
@@ -10155,7 +10155,7 @@
         <v>4.0483086956521737</v>
       </c>
       <c r="AC69" s="8">
-        <v>11.990809</v>
+        <v>11.346957</v>
       </c>
       <c r="AD69" s="8">
         <v>19.249325675675674</v>
@@ -10286,7 +10286,7 @@
         <v>2.9322702127659572</v>
       </c>
       <c r="AC70" s="8">
-        <v>5.5788580000000003</v>
+        <v>5.7217659999999997</v>
       </c>
       <c r="AD70" s="8">
         <v>10.327168493150685</v>
@@ -10937,7 +10937,7 @@
         <v>3.6627455882352939</v>
       </c>
       <c r="AC75" s="8">
-        <v>8.2385409999999997</v>
+        <v>9.3112949999999994</v>
       </c>
       <c r="AD75" s="8">
         <v>17.160295588235297</v>
@@ -11066,7 +11066,7 @@
         <v>2.6906021276595742</v>
       </c>
       <c r="AC76" s="8">
-        <v>7.4971430000000003</v>
+        <v>7.4951850000000002</v>
       </c>
       <c r="AD76" s="8">
         <v>14.298244736842106</v>
@@ -11290,7 +11290,7 @@
         <v>3.8066212328767124</v>
       </c>
       <c r="AC78" s="8">
-        <v>7.3374959999999998</v>
+        <v>6.5949869999999997</v>
       </c>
       <c r="AD78" s="8">
         <v>13.551256164383561</v>
@@ -11421,7 +11421,7 @@
         <v>3.0309523809523808</v>
       </c>
       <c r="AC79" s="8">
-        <v>11.280127999999999</v>
+        <v>10.376049999999999</v>
       </c>
       <c r="AD79" s="8">
         <v>16.067435384615383</v>
@@ -11552,7 +11552,7 @@
         <v>12.876582278481013</v>
       </c>
       <c r="AC80" s="8">
-        <v>16.469566</v>
+        <v>18.866655999999999</v>
       </c>
       <c r="AD80" s="8">
         <v>24.055303409090911</v>
@@ -11812,7 +11812,7 @@
         <v>12.569167</v>
       </c>
       <c r="AC82" s="8">
-        <v>18.385311000000002</v>
+        <v>18.220963000000001</v>
       </c>
       <c r="AD82" s="8">
         <v>25.003795049504951</v>
@@ -12074,7 +12074,7 @@
         <v>4.6142364583333331</v>
       </c>
       <c r="AC84" s="8">
-        <v>10.065001000000001</v>
+        <v>10.347899</v>
       </c>
       <c r="AD84" s="8">
         <v>15.921121782178218</v>
@@ -12560,7 +12560,7 @@
         <v>10.627881308411213</v>
       </c>
       <c r="AC88" s="8">
-        <v>16.475403</v>
+        <v>16.018467000000001</v>
       </c>
       <c r="AD88" s="8">
         <v>22.859413888888888</v>
@@ -12782,7 +12782,7 @@
         <v>11.709411764705882</v>
       </c>
       <c r="AC90" s="8">
-        <v>19.157969999999999</v>
+        <v>17.429607000000001</v>
       </c>
       <c r="AD90" s="8">
         <v>25.362156470588236</v>
@@ -13135,7 +13135,7 @@
         <v>6.0424426666666671</v>
       </c>
       <c r="AC93" s="8">
-        <v>11.871547</v>
+        <v>11.423797</v>
       </c>
       <c r="AD93" s="8">
         <v>16.720132673267326</v>
@@ -13264,7 +13264,7 @@
         <v>1.2730915662650604</v>
       </c>
       <c r="AC94" s="8">
-        <v>3.3222459999999998</v>
+        <v>3.2859950000000002</v>
       </c>
       <c r="AD94" s="8">
         <v>12.76014456521739</v>
@@ -13395,7 +13395,7 @@
         <v>3.8722759615384614</v>
       </c>
       <c r="AC95" s="8">
-        <v>7.2027869999999998</v>
+        <v>6.9703400000000002</v>
       </c>
       <c r="AD95" s="8">
         <v>14.590520183486239</v>
@@ -13526,7 +13526,7 @@
         <v>6.2952054794520551</v>
       </c>
       <c r="AC96" s="8">
-        <v>10.356555999999999</v>
+        <v>8.9574409999999993</v>
       </c>
       <c r="AD96" s="8">
         <v>16.435064935064936</v>
@@ -13786,7 +13786,7 @@
         <v>5.6586519230769232</v>
       </c>
       <c r="AC98" s="8">
-        <v>9.2755980000000005</v>
+        <v>8.1566919999999996</v>
       </c>
       <c r="AD98" s="8">
         <v>11.093652380952381</v>
@@ -13917,7 +13917,7 @@
         <v>8.7839872549019606</v>
       </c>
       <c r="AC99" s="8">
-        <v>17.345053</v>
+        <v>17.620336000000002</v>
       </c>
       <c r="AD99" s="8">
         <v>23.137826086956522</v>
@@ -14046,7 +14046,7 @@
         <v>9.1159918918918912</v>
       </c>
       <c r="AC100" s="8">
-        <v>13.694478</v>
+        <v>13.405901999999999</v>
       </c>
       <c r="AD100" s="8">
         <v>20.881578947368421</v>
@@ -14175,7 +14175,7 @@
         <v>13.030227118644069</v>
       </c>
       <c r="AC101" s="8">
-        <v>21.084054999999999</v>
+        <v>19.921551000000001</v>
       </c>
       <c r="AD101" s="8">
         <v>23.679777333333334</v>
@@ -14437,7 +14437,7 @@
         <v>5.064436942675159</v>
       </c>
       <c r="AC103" s="8">
-        <v>7.0817240000000004</v>
+        <v>7.745965</v>
       </c>
       <c r="AD103" s="8">
         <v>15.687367515923569</v>
@@ -14961,7 +14961,7 @@
         <v>7.8612326086956514</v>
       </c>
       <c r="AC107" s="8">
-        <v>13.677272</v>
+        <v>12.680071</v>
       </c>
       <c r="AD107" s="8">
         <v>22.62427608695652</v>
@@ -15092,7 +15092,7 @@
         <v>4.8374999999999995</v>
       </c>
       <c r="AC108" s="8">
-        <v>11.425782999999999</v>
+        <v>11.226955</v>
       </c>
       <c r="AD108" s="8">
         <v>17.172448979591838</v>
@@ -15223,7 +15223,7 @@
         <v>7.2509263888888889</v>
       </c>
       <c r="AC109" s="8">
-        <v>12.729628999999999</v>
+        <v>12.150010999999999</v>
       </c>
       <c r="AD109" s="8">
         <v>19.058102777777776</v>
@@ -15354,7 +15354,7 @@
         <v>11.43061224489796</v>
       </c>
       <c r="AC110" s="8">
-        <v>14.118926</v>
+        <v>15.831149</v>
       </c>
       <c r="AD110" s="8">
         <v>20.020833333333332</v>
@@ -15745,7 +15745,7 @@
         <v>11.302652272727274</v>
       </c>
       <c r="AC113" s="8">
-        <v>16.601430000000001</v>
+        <v>18.175567000000001</v>
       </c>
       <c r="AD113" s="8">
         <v>21.652082142857143</v>
@@ -15876,7 +15876,7 @@
         <v>10.924573076923078</v>
       </c>
       <c r="AC114" s="8">
-        <v>19.305498</v>
+        <v>19.245822</v>
       </c>
       <c r="AD114" s="8">
         <v>26.136873749999999</v>
@@ -16007,7 +16007,7 @@
         <v>3.4648707692307692</v>
       </c>
       <c r="AC115" s="8">
-        <v>6.6042500000000004</v>
+        <v>6.7923960000000001</v>
       </c>
       <c r="AD115" s="8">
         <v>13.677525757575756</v>
@@ -16267,7 +16267,7 @@
         <v>3.1139806451612904</v>
       </c>
       <c r="AC117" s="8">
-        <v>10.815844999999999</v>
+        <v>10.492899</v>
       </c>
       <c r="AD117" s="8">
         <v>17.603761290322581</v>
@@ -16527,7 +16527,7 @@
         <v>3.4925589285714289</v>
       </c>
       <c r="AC119" s="8">
-        <v>7.3045809999999998</v>
+        <v>6.7589759999999997</v>
       </c>
       <c r="AD119" s="8">
         <v>11.604725373134329</v>
@@ -17009,7 +17009,7 @@
         <v>1.8436030303030302</v>
       </c>
       <c r="AC123" s="8">
-        <v>4.1180830000000004</v>
+        <v>4.1625449999999997</v>
       </c>
       <c r="AD123" s="8">
         <v>10.993514285714285</v>
@@ -17402,7 +17402,7 @@
         <v>2.4333324324324321</v>
       </c>
       <c r="AC126" s="8">
-        <v>6.855925</v>
+        <v>6.9213959999999997</v>
       </c>
       <c r="AD126" s="8">
         <v>13.869594594594593</v>
@@ -18319,7 +18319,7 @@
         <v>11.309957861635221</v>
       </c>
       <c r="AC133" s="8">
-        <v>14.709037</v>
+        <v>16.024155</v>
       </c>
       <c r="AD133" s="8">
         <v>23.660185185185185</v>
@@ -18545,7 +18545,7 @@
         <v>4.5395061728395056</v>
       </c>
       <c r="AC135" s="8">
-        <v>10.675162</v>
+        <v>9.7676949999999998</v>
       </c>
       <c r="AD135" s="8">
         <v>16.546342682926827</v>
@@ -18676,7 +18676,7 @@
         <v>5.3064949152542367</v>
       </c>
       <c r="AC136" s="8">
-        <v>9.2728780000000004</v>
+        <v>9.8814969999999995</v>
       </c>
       <c r="AD136" s="8">
         <v>14.840540540540541</v>
@@ -18807,7 +18807,7 @@
         <v>2.7550976470588235</v>
       </c>
       <c r="AC137" s="8">
-        <v>6.1336060000000003</v>
+        <v>6.6515680000000001</v>
       </c>
       <c r="AD137" s="8">
         <v>13.568823529411764</v>
@@ -19065,7 +19065,7 @@
         <v>6.0578613207547169</v>
       </c>
       <c r="AC139" s="8">
-        <v>11.057862999999999</v>
+        <v>11.981069</v>
       </c>
       <c r="AD139" s="8">
         <v>18.844236448598132</v>
@@ -19321,7 +19321,7 @@
         <v>9.4043103448275875</v>
       </c>
       <c r="AC141" s="8">
-        <v>14.381779999999999</v>
+        <v>14.391406</v>
       </c>
       <c r="AD141" s="8">
         <v>21.6655737704918</v>
@@ -19583,7 +19583,7 @@
         <v>11.926557142857144</v>
       </c>
       <c r="AC143" s="8">
-        <v>18.838045000000001</v>
+        <v>18.335062000000001</v>
       </c>
       <c r="AD143" s="8">
         <v>24.421007291666669</v>
@@ -19714,7 +19714,7 @@
         <v>2.7355962962962965</v>
       </c>
       <c r="AC144" s="8">
-        <v>7.6360200000000003</v>
+        <v>7.0341550000000002</v>
       </c>
       <c r="AD144" s="8">
         <v>13.948970370370372</v>
@@ -19845,7 +19845,7 @@
         <v>15.889166666666666</v>
       </c>
       <c r="AC145" s="8">
-        <v>17.436140999999999</v>
+        <v>19.187843000000001</v>
       </c>
       <c r="AD145" s="8">
         <v>25.526345161290322</v>
@@ -20369,7 +20369,7 @@
         <v>3.3331578947368419</v>
       </c>
       <c r="AC149" s="8">
-        <v>7.9299530000000003</v>
+        <v>7.8896290000000002</v>
       </c>
       <c r="AD149" s="8">
         <v>14.36763786407767</v>
@@ -20631,7 +20631,7 @@
         <v>10.91741343283582</v>
       </c>
       <c r="AC151" s="8">
-        <v>14.939235</v>
+        <v>16.213431</v>
       </c>
       <c r="AD151" s="8">
         <v>23.148755223880595</v>
@@ -21153,7 +21153,7 @@
         <v>6.0188277777777781</v>
       </c>
       <c r="AC155" s="8">
-        <v>9.8894140000000004</v>
+        <v>9.8302300000000002</v>
       </c>
       <c r="AD155" s="8">
         <v>16.574241818181818</v>
@@ -21542,7 +21542,7 @@
         <v>11.15351052631579</v>
       </c>
       <c r="AC158" s="8">
-        <v>20.425224</v>
+        <v>20.074998999999998</v>
       </c>
       <c r="AD158" s="8">
         <v>28.032455263157896</v>
@@ -21673,7 +21673,7 @@
         <v>7.951851111111111</v>
       </c>
       <c r="AC159" s="8">
-        <v>18.755756000000002</v>
+        <v>15.061995</v>
       </c>
       <c r="AD159" s="8">
         <v>22.998519999999999</v>
@@ -21804,7 +21804,7 @@
         <v>6.2339175438596497</v>
       </c>
       <c r="AC160" s="8">
-        <v>12.361627</v>
+        <v>10.781969</v>
       </c>
       <c r="AD160" s="8">
         <v>16.261903896103895</v>
@@ -22197,7 +22197,7 @@
         <v>7.9048343511450385</v>
       </c>
       <c r="AC163" s="8">
-        <v>12.922331</v>
+        <v>13.818740999999999</v>
       </c>
       <c r="AD163" s="8">
         <v>21.11979932885906</v>
@@ -23078,7 +23078,7 @@
         <v>4.7345776119402982</v>
       </c>
       <c r="AC170" s="8">
-        <v>9.3863149999999997</v>
+        <v>8.7879780000000007</v>
       </c>
       <c r="AD170" s="8">
         <v>12.63639387755102</v>
@@ -23209,7 +23209,7 @@
         <v>7.314473684210526</v>
       </c>
       <c r="AC171" s="8">
-        <v>10.849073000000001</v>
+        <v>10.524559999999999</v>
       </c>
       <c r="AD171" s="8">
         <v>17.484210526315788</v>
@@ -23729,7 +23729,7 @@
         <v>4.3872588235294119</v>
       </c>
       <c r="AC175" s="8">
-        <v>10.383055000000001</v>
+        <v>10.198365000000001</v>
       </c>
       <c r="AD175" s="8">
         <v>16.807405555555555</v>
@@ -23860,7 +23860,7 @@
         <v>5.4822152439024388</v>
       </c>
       <c r="AC176" s="8">
-        <v>7.9571040000000002</v>
+        <v>7.9408969999999997</v>
       </c>
       <c r="AD176" s="8">
         <v>14.779718674698795</v>
@@ -24122,7 +24122,7 @@
         <v>6.9505045454545451</v>
       </c>
       <c r="AC178" s="8">
-        <v>11.352039</v>
+        <v>11.242238</v>
       </c>
       <c r="AD178" s="8">
         <v>17.735783823529413</v>
@@ -24511,7 +24511,7 @@
         <v>6.9740746031746026</v>
       </c>
       <c r="AC181" s="8">
-        <v>14.172348</v>
+        <v>14.961313000000001</v>
       </c>
       <c r="AD181" s="8">
         <v>21.595832812499999</v>
